--- a/eval/nbfc_retrieval_test_questions_results_v1.xlsx
+++ b/eval/nbfc_retrieval_test_questions_results_v1.xlsx
@@ -1694,12 +1694,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>no numeric facts to compare - read the answer yourself</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>no numeric facts to compare - read the answer yourself</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>none of the expected figures appear (30, 2025.)</t>
         </is>
       </c>
       <c r="J42" t="n">

--- a/eval/nbfc_retrieval_test_questions_results_v1.xlsx
+++ b/eval/nbfc_retrieval_test_questions_results_v1.xlsx
@@ -1055,12 +1055,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>no numeric facts to compare - read the answer yourself</t>
+          <t>declined to answer an in-scope question - retrieval likely missed</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>no numeric facts to compare - read the answer yourself</t>
+          <t>declined to answer an in-scope question - retrieval likely missed</t>
         </is>
       </c>
       <c r="J28" t="n">
